--- a/static/files/products_import_template.xlsx
+++ b/static/files/products_import_template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adeba\OneDrive\Desktop\clinic365\static\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev3\clinic365\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="102">
   <si>
     <t>product_name</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>K1222</t>
+  </si>
+  <si>
+    <t>unit</t>
   </si>
 </sst>
 </file>
@@ -644,21 +647,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,22 +682,25 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -707,30 +714,30 @@
         <v>1000</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>13</v>
       </c>
-      <c r="H2" t="str">
-        <f t="shared" ref="H2:H3" si="0">TEXT("2025-08-20","YYYY-MM-DD")</f>
+      <c r="I2" t="str">
+        <f t="shared" ref="I2:I3" si="0">TEXT("2025-08-20","YYYY-MM-DD")</f>
         <v>2025-08-20</v>
       </c>
-      <c r="I2" t="str">
-        <f t="shared" ref="I2:I3" si="1">TEXT("2025-09-29","YYYY-MM-DD")</f>
+      <c r="J2" t="str">
+        <f t="shared" ref="J2:J3" si="1">TEXT("2025-09-29","YYYY-MM-DD")</f>
         <v>2025-09-29</v>
       </c>
-      <c r="J2">
-        <v>11</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="K2">
+        <v>11</v>
+      </c>
+      <c r="L2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -744,30 +751,30 @@
         <v>1000</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>10</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <f t="shared" si="0"/>
         <v>2025-08-20</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <f t="shared" si="1"/>
         <v>2025-09-29</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>6</v>
       </c>
-      <c r="K3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -778,30 +785,30 @@
         <v>4000</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>5</v>
       </c>
-      <c r="H4" t="str">
-        <f t="shared" ref="H4:H6" si="2">TEXT("2025-12-20","YYYY-MM-DD")</f>
+      <c r="I4" t="str">
+        <f t="shared" ref="I4:I6" si="2">TEXT("2025-12-20","YYYY-MM-DD")</f>
         <v>2025-12-20</v>
       </c>
-      <c r="I4" t="str">
-        <f t="shared" ref="I4:I6" si="3">TEXT("2026-01-12","YYYY-MM-DD")</f>
+      <c r="J4" t="str">
+        <f t="shared" ref="J4:J6" si="3">TEXT("2026-01-12","YYYY-MM-DD")</f>
         <v>2026-01-12</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>8</v>
       </c>
-      <c r="K4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -812,30 +819,30 @@
         <v>1000</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>5</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <f t="shared" si="2"/>
         <v>2025-12-20</v>
       </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
         <f t="shared" si="3"/>
         <v>2026-01-12</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>2</v>
       </c>
-      <c r="K5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -846,30 +853,30 @@
         <v>1500</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>5</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <f t="shared" si="2"/>
         <v>2025-12-20</v>
       </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
         <f t="shared" si="3"/>
         <v>2026-01-12</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>13</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -880,30 +887,30 @@
         <v>800</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F7" t="s">
         <v>19</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>6</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <f>TEXT("2025-12-12","YYYY-MM-DD")</f>
         <v>2025-12-12</v>
       </c>
-      <c r="I7" t="str">
+      <c r="J7" t="str">
         <f>TEXT("2026-05-20","YYYY-MM-DD")</f>
         <v>2026-05-20</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>3</v>
       </c>
-      <c r="K7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -914,30 +921,30 @@
         <v>60</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="H8" t="str">
-        <f t="shared" ref="H8:H9" si="4">TEXT("2025-12-12","YYYY-MM-DD")</f>
+      <c r="I8" t="str">
+        <f t="shared" ref="I8:I9" si="4">TEXT("2025-12-12","YYYY-MM-DD")</f>
         <v>2025-12-12</v>
       </c>
-      <c r="I8" t="str">
-        <f t="shared" ref="I8:I9" si="5">TEXT("2026-05-20","YYYY-MM-DD")</f>
+      <c r="J8" t="str">
+        <f t="shared" ref="J8:J9" si="5">TEXT("2026-05-20","YYYY-MM-DD")</f>
         <v>2026-05-20</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>2</v>
       </c>
-      <c r="K8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -948,30 +955,30 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>10</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <f t="shared" si="4"/>
         <v>2025-12-12</v>
       </c>
-      <c r="I9" t="str">
+      <c r="J9" t="str">
         <f t="shared" si="5"/>
         <v>2026-05-20</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>2</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -982,30 +989,30 @@
         <v>10000</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F10" t="s">
         <v>19</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>10</v>
       </c>
-      <c r="H10" t="str">
-        <f t="shared" ref="H10" si="6">TEXT("2025-08-20","YYYY-MM-DD")</f>
+      <c r="I10" t="str">
+        <f t="shared" ref="I10" si="6">TEXT("2025-08-20","YYYY-MM-DD")</f>
         <v>2025-08-20</v>
       </c>
-      <c r="I10" t="str">
-        <f t="shared" ref="I10" si="7">TEXT("2025-09-29","YYYY-MM-DD")</f>
+      <c r="J10" t="str">
+        <f t="shared" ref="J10" si="7">TEXT("2025-09-29","YYYY-MM-DD")</f>
         <v>2025-09-29</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>3</v>
       </c>
-      <c r="K10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1016,30 +1023,33 @@
         <v>2000</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11">
+        <v>200</v>
+      </c>
+      <c r="H11">
         <v>15</v>
       </c>
-      <c r="H11" t="str">
-        <f t="shared" ref="H11:H12" si="8">TEXT("2025-12-20","YYYY-MM-DD")</f>
+      <c r="I11" t="str">
+        <f t="shared" ref="I11:I12" si="8">TEXT("2025-12-20","YYYY-MM-DD")</f>
         <v>2025-12-20</v>
       </c>
-      <c r="I11" t="str">
-        <f t="shared" ref="I11:I12" si="9">TEXT("2026-01-12","YYYY-MM-DD")</f>
+      <c r="J11" t="str">
+        <f t="shared" ref="J11:J12" si="9">TEXT("2026-01-12","YYYY-MM-DD")</f>
         <v>2026-01-12</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>1</v>
       </c>
-      <c r="K11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -1050,30 +1060,30 @@
         <v>1200</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>5</v>
       </c>
-      <c r="H12" t="str">
+      <c r="I12" t="str">
         <f t="shared" si="8"/>
         <v>2025-12-20</v>
       </c>
-      <c r="I12" t="str">
+      <c r="J12" t="str">
         <f t="shared" si="9"/>
         <v>2026-01-12</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>3</v>
       </c>
-      <c r="K12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -1084,30 +1094,30 @@
         <v>1000</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>10</v>
       </c>
-      <c r="H13" t="str">
-        <f t="shared" ref="H13:H20" si="10">TEXT("2025-12-12","YYYY-MM-DD")</f>
+      <c r="I13" t="str">
+        <f t="shared" ref="I13:I20" si="10">TEXT("2025-12-12","YYYY-MM-DD")</f>
         <v>2025-12-12</v>
       </c>
-      <c r="I13" t="str">
-        <f t="shared" ref="I13:I20" si="11">TEXT("2026-05-20","YYYY-MM-DD")</f>
+      <c r="J13" t="str">
+        <f t="shared" ref="J13:J20" si="11">TEXT("2026-05-20","YYYY-MM-DD")</f>
         <v>2026-05-20</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>2</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1118,30 +1128,30 @@
         <v>250</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F14" t="s">
         <v>19</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>7</v>
       </c>
-      <c r="H14" t="str">
+      <c r="I14" t="str">
         <f t="shared" si="10"/>
         <v>2025-12-12</v>
       </c>
-      <c r="I14" t="str">
+      <c r="J14" t="str">
         <f t="shared" si="11"/>
         <v>2026-05-20</v>
       </c>
-      <c r="J14">
-        <v>11</v>
-      </c>
-      <c r="K14" t="s">
+      <c r="K14">
+        <v>11</v>
+      </c>
+      <c r="L14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1152,30 +1162,30 @@
         <v>4500</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>5</v>
       </c>
-      <c r="H15" t="str">
+      <c r="I15" t="str">
         <f t="shared" si="10"/>
         <v>2025-12-12</v>
       </c>
-      <c r="I15" t="str">
+      <c r="J15" t="str">
         <f t="shared" si="11"/>
         <v>2026-05-20</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>8</v>
       </c>
-      <c r="K15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -1186,30 +1196,30 @@
         <v>200</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>5</v>
       </c>
-      <c r="H16" t="str">
+      <c r="I16" t="str">
         <f t="shared" si="10"/>
         <v>2025-12-12</v>
       </c>
-      <c r="I16" t="str">
+      <c r="J16" t="str">
         <f t="shared" si="11"/>
         <v>2026-05-20</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>2</v>
       </c>
-      <c r="K16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1220,30 +1230,33 @@
         <v>60</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
       </c>
       <c r="G17">
+        <v>210</v>
+      </c>
+      <c r="H17">
         <v>15</v>
       </c>
-      <c r="H17" t="str">
+      <c r="I17" t="str">
         <f t="shared" si="10"/>
         <v>2025-12-12</v>
       </c>
-      <c r="I17" t="str">
+      <c r="J17" t="str">
         <f t="shared" si="11"/>
         <v>2026-05-20</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>1</v>
       </c>
-      <c r="K17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -1254,30 +1267,30 @@
         <v>500</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>10</v>
       </c>
-      <c r="H18" t="str">
+      <c r="I18" t="str">
         <f t="shared" si="10"/>
         <v>2025-12-12</v>
       </c>
-      <c r="I18" t="str">
+      <c r="J18" t="str">
         <f t="shared" si="11"/>
         <v>2026-05-20</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>2</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -1288,30 +1301,30 @@
         <v>500</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F19" t="s">
         <v>19</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>7</v>
       </c>
-      <c r="H19" t="str">
+      <c r="I19" t="str">
         <f t="shared" si="10"/>
         <v>2025-12-12</v>
       </c>
-      <c r="I19" t="str">
+      <c r="J19" t="str">
         <f t="shared" si="11"/>
         <v>2026-05-20</v>
       </c>
-      <c r="J19">
-        <v>11</v>
-      </c>
-      <c r="K19" t="s">
+      <c r="K19">
+        <v>11</v>
+      </c>
+      <c r="L19" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1322,30 +1335,30 @@
         <v>50</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>5</v>
       </c>
-      <c r="H20" t="str">
+      <c r="I20" t="str">
         <f t="shared" si="10"/>
         <v>2025-12-12</v>
       </c>
-      <c r="I20" t="str">
+      <c r="J20" t="str">
         <f t="shared" si="11"/>
         <v>2026-05-20</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>8</v>
       </c>
-      <c r="K20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -1356,30 +1369,30 @@
         <v>500</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F21" t="s">
         <v>15</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>13</v>
       </c>
-      <c r="H21" t="str">
-        <f t="shared" ref="H21:H23" si="12">TEXT("2025-12-20","YYYY-MM-DD")</f>
+      <c r="I21" t="str">
+        <f t="shared" ref="I21:I23" si="12">TEXT("2025-12-20","YYYY-MM-DD")</f>
         <v>2025-12-20</v>
       </c>
-      <c r="I21" t="str">
-        <f t="shared" ref="I21:I26" si="13">TEXT("2026-07-20","YYYY-MM-DD")</f>
+      <c r="J21" t="str">
+        <f t="shared" ref="J21:J26" si="13">TEXT("2026-07-20","YYYY-MM-DD")</f>
         <v>2026-07-20</v>
       </c>
-      <c r="J21">
-        <v>11</v>
-      </c>
-      <c r="K21" t="s">
+      <c r="K21">
+        <v>11</v>
+      </c>
+      <c r="L21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1390,30 +1403,30 @@
         <v>60</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F22" t="s">
         <v>17</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>5</v>
       </c>
-      <c r="H22" t="str">
+      <c r="I22" t="str">
         <f t="shared" si="12"/>
         <v>2025-12-20</v>
       </c>
-      <c r="I22" t="str">
+      <c r="J22" t="str">
         <f t="shared" si="13"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>4</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -1424,30 +1437,30 @@
         <v>1000</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F23" t="s">
         <v>19</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>5</v>
       </c>
-      <c r="H23" t="str">
+      <c r="I23" t="str">
         <f t="shared" si="12"/>
         <v>2025-12-20</v>
       </c>
-      <c r="I23" t="str">
+      <c r="J23" t="str">
         <f t="shared" si="13"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>5</v>
       </c>
-      <c r="K23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -1458,30 +1471,30 @@
         <v>25000</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F24" t="s">
         <v>14</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>10</v>
       </c>
-      <c r="H24" t="str">
-        <f t="shared" ref="H24:H26" si="14">TEXT("2025-12-12","YYYY-MM-DD")</f>
+      <c r="I24" t="str">
+        <f t="shared" ref="I24:I26" si="14">TEXT("2025-12-12","YYYY-MM-DD")</f>
         <v>2025-12-12</v>
       </c>
-      <c r="I24" t="str">
+      <c r="J24" t="str">
         <f t="shared" si="13"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>2</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>43</v>
       </c>
@@ -1492,30 +1505,30 @@
         <v>25000</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F25" t="s">
         <v>15</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>7</v>
       </c>
-      <c r="H25" t="str">
+      <c r="I25" t="str">
         <f t="shared" si="14"/>
         <v>2025-12-12</v>
       </c>
-      <c r="I25" t="str">
+      <c r="J25" t="str">
         <f t="shared" si="13"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>4</v>
       </c>
-      <c r="K25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>44</v>
       </c>
@@ -1526,30 +1539,30 @@
         <v>15000</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F26" t="s">
         <v>19</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>7</v>
       </c>
-      <c r="H26" t="str">
+      <c r="I26" t="str">
         <f t="shared" si="14"/>
         <v>2025-12-12</v>
       </c>
-      <c r="I26" t="str">
+      <c r="J26" t="str">
         <f t="shared" si="13"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J26">
-        <v>11</v>
-      </c>
-      <c r="K26" t="s">
+      <c r="K26">
+        <v>11</v>
+      </c>
+      <c r="L26" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>45</v>
       </c>
@@ -1560,30 +1573,30 @@
         <v>200</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F27" t="s">
         <v>16</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>5</v>
       </c>
-      <c r="H27" t="str">
-        <f t="shared" ref="H27" si="15">TEXT("2025-08-20","YYYY-MM-DD")</f>
+      <c r="I27" t="str">
+        <f t="shared" ref="I27" si="15">TEXT("2025-08-20","YYYY-MM-DD")</f>
         <v>2025-08-20</v>
       </c>
-      <c r="I27" t="str">
-        <f t="shared" ref="I27:I35" si="16">TEXT("2026-07-20","YYYY-MM-DD")</f>
+      <c r="J27" t="str">
+        <f t="shared" ref="J27:J35" si="16">TEXT("2026-07-20","YYYY-MM-DD")</f>
         <v>2026-07-20</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>3</v>
       </c>
-      <c r="K27" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>46</v>
       </c>
@@ -1594,30 +1607,30 @@
         <v>161</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>15</v>
       </c>
-      <c r="H28" t="str">
-        <f t="shared" ref="H28:H32" si="17">TEXT("2025-08-20","YYYY-MM-DD")</f>
+      <c r="I28" t="str">
+        <f t="shared" ref="I28:I32" si="17">TEXT("2025-08-20","YYYY-MM-DD")</f>
         <v>2025-08-20</v>
       </c>
-      <c r="I28" t="str">
+      <c r="J28" t="str">
         <f t="shared" si="16"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>1</v>
       </c>
-      <c r="K28" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>47</v>
       </c>
@@ -1628,30 +1641,30 @@
         <v>3000</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F29" t="s">
         <v>19</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>5</v>
       </c>
-      <c r="H29" t="str">
+      <c r="I29" t="str">
         <f t="shared" si="17"/>
         <v>2025-08-20</v>
       </c>
-      <c r="I29" t="str">
+      <c r="J29" t="str">
         <f t="shared" si="16"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>5</v>
       </c>
-      <c r="K29" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>48</v>
       </c>
@@ -1662,30 +1675,30 @@
         <v>300</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F30" t="s">
         <v>15</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>7</v>
       </c>
-      <c r="H30" t="str">
+      <c r="I30" t="str">
         <f t="shared" si="17"/>
         <v>2025-08-20</v>
       </c>
-      <c r="I30" t="str">
+      <c r="J30" t="str">
         <f t="shared" si="16"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>4</v>
       </c>
-      <c r="K30" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>49</v>
       </c>
@@ -1696,30 +1709,30 @@
         <v>50</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F31" t="s">
         <v>16</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>5</v>
       </c>
-      <c r="H31" t="str">
+      <c r="I31" t="str">
         <f t="shared" si="17"/>
         <v>2025-08-20</v>
       </c>
-      <c r="I31" t="str">
+      <c r="J31" t="str">
         <f t="shared" si="16"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>2</v>
       </c>
-      <c r="K31" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>50</v>
       </c>
@@ -1730,30 +1743,30 @@
         <v>1000</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>5</v>
       </c>
-      <c r="H32" t="str">
+      <c r="I32" t="str">
         <f t="shared" si="17"/>
         <v>2025-08-20</v>
       </c>
-      <c r="I32" t="str">
+      <c r="J32" t="str">
         <f t="shared" si="16"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>13</v>
       </c>
-      <c r="K32" t="s">
+      <c r="L32" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>51</v>
       </c>
@@ -1764,30 +1777,30 @@
         <v>2000</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F33" t="s">
         <v>19</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>6</v>
       </c>
-      <c r="H33" t="str">
+      <c r="I33" t="str">
         <f>TEXT("2025-12-20","YYYY-MM-DD")</f>
         <v>2025-12-20</v>
       </c>
-      <c r="I33" t="str">
+      <c r="J33" t="str">
         <f t="shared" si="16"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>3</v>
       </c>
-      <c r="K33" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>52</v>
       </c>
@@ -1798,30 +1811,30 @@
         <v>20020</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>10</v>
       </c>
-      <c r="H34" t="str">
-        <f t="shared" ref="H34:H35" si="18">TEXT("2025-12-20","YYYY-MM-DD")</f>
+      <c r="I34" t="str">
+        <f t="shared" ref="I34:I35" si="18">TEXT("2025-12-20","YYYY-MM-DD")</f>
         <v>2025-12-20</v>
       </c>
-      <c r="I34" t="str">
+      <c r="J34" t="str">
         <f t="shared" si="16"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>2</v>
       </c>
-      <c r="K34" t="s">
+      <c r="L34" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>53</v>
       </c>
@@ -1832,30 +1845,30 @@
         <v>50</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>7</v>
       </c>
-      <c r="H35" t="str">
+      <c r="I35" t="str">
         <f t="shared" si="18"/>
         <v>2025-12-20</v>
       </c>
-      <c r="I35" t="str">
+      <c r="J35" t="str">
         <f t="shared" si="16"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J35">
-        <v>11</v>
-      </c>
-      <c r="K35" t="s">
+      <c r="K35">
+        <v>11</v>
+      </c>
+      <c r="L35" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>54</v>
       </c>
@@ -1866,30 +1879,30 @@
         <v>2000</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F36" t="s">
         <v>19</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>6</v>
       </c>
-      <c r="H36" t="str">
+      <c r="I36" t="str">
         <f>TEXT("2025-12-20","YYYY-MM-DD")</f>
         <v>2025-12-20</v>
       </c>
-      <c r="I36" t="str">
-        <f t="shared" ref="I36:I41" si="19">TEXT("2026-07-20","YYYY-MM-DD")</f>
+      <c r="J36" t="str">
+        <f t="shared" ref="J36:J41" si="19">TEXT("2026-07-20","YYYY-MM-DD")</f>
         <v>2026-07-20</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>3</v>
       </c>
-      <c r="K36" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>55</v>
       </c>
@@ -1900,30 +1913,30 @@
         <v>100</v>
       </c>
       <c r="E37">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F37" t="s">
         <v>19</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>10</v>
       </c>
-      <c r="H37" t="str">
-        <f t="shared" ref="H37:H39" si="20">TEXT("2025-12-20","YYYY-MM-DD")</f>
+      <c r="I37" t="str">
+        <f t="shared" ref="I37:I39" si="20">TEXT("2025-12-20","YYYY-MM-DD")</f>
         <v>2025-12-20</v>
       </c>
-      <c r="I37" t="str">
+      <c r="J37" t="str">
         <f t="shared" si="19"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>3</v>
       </c>
-      <c r="K37" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>56</v>
       </c>
@@ -1934,30 +1947,30 @@
         <v>500</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F38" t="s">
         <v>15</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>13</v>
       </c>
-      <c r="H38" t="str">
+      <c r="I38" t="str">
         <f t="shared" si="20"/>
         <v>2025-12-20</v>
       </c>
-      <c r="I38" t="str">
+      <c r="J38" t="str">
         <f t="shared" si="19"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J38">
-        <v>11</v>
-      </c>
-      <c r="K38" t="s">
+      <c r="K38">
+        <v>11</v>
+      </c>
+      <c r="L38" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>57</v>
       </c>
@@ -1968,30 +1981,30 @@
         <v>600</v>
       </c>
       <c r="E39">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F39" t="s">
         <v>16</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>5</v>
       </c>
-      <c r="H39" t="str">
+      <c r="I39" t="str">
         <f t="shared" si="20"/>
         <v>2025-12-20</v>
       </c>
-      <c r="I39" t="str">
+      <c r="J39" t="str">
         <f t="shared" si="19"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>2</v>
       </c>
-      <c r="K39" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>58</v>
       </c>
@@ -2002,30 +2015,30 @@
         <v>2000</v>
       </c>
       <c r="E40">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F40" t="s">
         <v>18</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>10</v>
       </c>
-      <c r="H40" t="str">
+      <c r="I40" t="str">
         <f>TEXT("2025-05-20","YYYY-MM-DD")</f>
         <v>2025-05-20</v>
       </c>
-      <c r="I40" t="str">
+      <c r="J40" t="str">
         <f t="shared" si="19"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>2</v>
       </c>
-      <c r="K40" t="s">
+      <c r="L40" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>59</v>
       </c>
@@ -2036,26 +2049,26 @@
         <v>2000</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F41" t="s">
         <v>19</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>10</v>
       </c>
-      <c r="H41" t="str">
-        <f t="shared" ref="H41" si="21">TEXT("2025-08-20","YYYY-MM-DD")</f>
+      <c r="I41" t="str">
+        <f t="shared" ref="I41" si="21">TEXT("2025-08-20","YYYY-MM-DD")</f>
         <v>2025-08-20</v>
       </c>
-      <c r="I41" t="str">
+      <c r="J41" t="str">
         <f t="shared" si="19"/>
         <v>2026-07-20</v>
       </c>
-      <c r="J41">
+      <c r="K41">
         <v>3</v>
       </c>
-      <c r="K41" t="s">
+      <c r="L41" t="s">
         <v>11</v>
       </c>
     </row>
